--- a/PFE/NEW/PFE_base_to_view_mapping.xlsx
+++ b/PFE/NEW/PFE_base_to_view_mapping.xlsx
@@ -1026,7 +1026,7 @@
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Direct value (cleaned to number, safe-cast to DOUBLE); from the 'IM' product_group, CARTOR source. Initial margin (source definition pending confirmation).</t>
+          <t>Direct value (cleaned to number, safe-cast to DOUBLE); from product_group='IM', CARTOR source (max_usage_0_3_mo, the 0-3 month bucket). Initial margin. Source definition (value doubles under stress) pending data-owner confirmation.</t>
         </is>
       </c>
     </row>
